--- a/recall_tables.xlsx
+++ b/recall_tables.xlsx
@@ -737,7 +737,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2018: pending — per-SNR matrices are being rebuilt from the checkpoints.</t>
+          <t>2018: not filled — 2018 work is parked (2026-10-06); Colab task rebuild_snr_2018 would fill it.</t>
         </is>
       </c>
     </row>
